--- a/APPT/data/output/Final_Production_Plan_2026-01-12.xlsx
+++ b/APPT/data/output/Final_Production_Plan_2026-01-12.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="378">
   <si>
     <t>Production Line</t>
   </si>
@@ -78,33 +78,27 @@
     <t>INTERNAL</t>
   </si>
   <si>
+    <t>INC1</t>
+  </si>
+  <si>
+    <t>INC4</t>
+  </si>
+  <si>
     <t>INT2</t>
   </si>
   <si>
-    <t>INC1</t>
-  </si>
-  <si>
-    <t>INC4</t>
-  </si>
-  <si>
     <t>INT3</t>
   </si>
   <si>
     <t>AUTO_1</t>
   </si>
   <si>
-    <t>910725376 + 910726630</t>
-  </si>
-  <si>
     <t>910721946</t>
   </si>
   <si>
     <t>910721918</t>
   </si>
   <si>
-    <t>910725305 + 910726648</t>
-  </si>
-  <si>
     <t>910721814</t>
   </si>
   <si>
@@ -168,6 +162,12 @@
     <t>910722223</t>
   </si>
   <si>
+    <t>910725376</t>
+  </si>
+  <si>
+    <t>910725305</t>
+  </si>
+  <si>
     <t>910725378</t>
   </si>
   <si>
@@ -189,45 +189,51 @@
     <t>910726580</t>
   </si>
   <si>
+    <t>910726648</t>
+  </si>
+  <si>
+    <t>910726630</t>
+  </si>
+  <si>
     <t>95619314</t>
   </si>
   <si>
+    <t>83900263</t>
+  </si>
+  <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>83900261</t>
+  </si>
+  <si>
+    <t>80880903</t>
+  </si>
+  <si>
+    <t>83900262</t>
+  </si>
+  <si>
+    <t>80879271</t>
+  </si>
+  <si>
+    <t>83900260</t>
+  </si>
+  <si>
+    <t>80880902</t>
+  </si>
+  <si>
+    <t>80841060</t>
+  </si>
+  <si>
+    <t>80851521</t>
+  </si>
+  <si>
     <t>80879278</t>
   </si>
   <si>
-    <t>83900263</t>
-  </si>
-  <si>
     <t>80879281</t>
   </si>
   <si>
-    <t>83900259</t>
-  </si>
-  <si>
-    <t>83900261</t>
-  </si>
-  <si>
-    <t>80880903</t>
-  </si>
-  <si>
-    <t>83900262</t>
-  </si>
-  <si>
-    <t>80879271</t>
-  </si>
-  <si>
-    <t>83900260</t>
-  </si>
-  <si>
-    <t>80880902</t>
-  </si>
-  <si>
-    <t>80841060</t>
-  </si>
-  <si>
-    <t>80851521</t>
-  </si>
-  <si>
     <t>80880880</t>
   </si>
   <si>
@@ -249,33 +255,39 @@
     <t>80895916</t>
   </si>
   <si>
+    <t>80879269</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
     <t>HC BASE</t>
   </si>
   <si>
+    <t>H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>H&amp;S SS</t>
+  </si>
+  <si>
+    <t>H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>PTN Silky Smooth Shampoo</t>
+  </si>
+  <si>
+    <t>PTN SS Conditioner</t>
+  </si>
+  <si>
     <t>PTN  Hair Fall Control</t>
   </si>
   <si>
-    <t>H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
     <t>PTN Lively Clean</t>
   </si>
   <si>
-    <t>H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>H&amp;S SS</t>
-  </si>
-  <si>
-    <t>H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>PTN Silky Smooth Shampoo</t>
-  </si>
-  <si>
-    <t>PTN SS Conditioner</t>
-  </si>
-  <si>
     <t>H&amp;S Deep Cleanse</t>
   </si>
   <si>
@@ -297,126 +309,132 @@
     <t>REP01-0112</t>
   </si>
   <si>
-    <t>CI434</t>
+    <t>CI437</t>
+  </si>
+  <si>
+    <t>CI438</t>
+  </si>
+  <si>
+    <t>CI440</t>
+  </si>
+  <si>
+    <t>CI442</t>
+  </si>
+  <si>
+    <t>CI445</t>
+  </si>
+  <si>
+    <t>REP02-0112</t>
+  </si>
+  <si>
+    <t>CI446</t>
+  </si>
+  <si>
+    <t>CI447</t>
+  </si>
+  <si>
+    <t>CI450</t>
+  </si>
+  <si>
+    <t>CI453</t>
+  </si>
+  <si>
+    <t>CI454</t>
+  </si>
+  <si>
+    <t>CI455</t>
+  </si>
+  <si>
+    <t>CI456</t>
+  </si>
+  <si>
+    <t>CI458</t>
+  </si>
+  <si>
+    <t>REP03-0112</t>
+  </si>
+  <si>
+    <t>CI460</t>
+  </si>
+  <si>
+    <t>CI461</t>
+  </si>
+  <si>
+    <t>CI462</t>
+  </si>
+  <si>
+    <t>CI463</t>
+  </si>
+  <si>
+    <t>CI465</t>
+  </si>
+  <si>
+    <t>CI466</t>
   </si>
   <si>
     <t>CI435</t>
   </si>
   <si>
+    <t>CI441</t>
+  </si>
+  <si>
     <t>CI436</t>
   </si>
   <si>
-    <t>CI437</t>
-  </si>
-  <si>
-    <t>CI438</t>
-  </si>
-  <si>
-    <t>CI440</t>
+    <t>CI439</t>
   </si>
   <si>
     <t>CI443</t>
   </si>
   <si>
-    <t>REP02-0112</t>
-  </si>
-  <si>
     <t>CI444</t>
   </si>
   <si>
-    <t>CI445</t>
-  </si>
-  <si>
     <t>CI448</t>
   </si>
   <si>
+    <t>CI449</t>
+  </si>
+  <si>
     <t>CI451</t>
   </si>
   <si>
     <t>CI452</t>
   </si>
   <si>
-    <t>CI453</t>
-  </si>
-  <si>
-    <t>CI454</t>
-  </si>
-  <si>
-    <t>CI456</t>
-  </si>
-  <si>
-    <t>REP03-0112</t>
-  </si>
-  <si>
     <t>CI457</t>
   </si>
   <si>
-    <t>CI458</t>
-  </si>
-  <si>
     <t>CI459</t>
   </si>
   <si>
-    <t>CI460</t>
-  </si>
-  <si>
-    <t>CI461</t>
-  </si>
-  <si>
-    <t>CI462</t>
-  </si>
-  <si>
-    <t>CI433</t>
-  </si>
-  <si>
-    <t>CI439</t>
-  </si>
-  <si>
-    <t>CI441</t>
-  </si>
-  <si>
-    <t>CI442</t>
-  </si>
-  <si>
-    <t>CI446</t>
-  </si>
-  <si>
-    <t>CI447</t>
-  </si>
-  <si>
-    <t>CI449</t>
-  </si>
-  <si>
-    <t>CI450</t>
-  </si>
-  <si>
-    <t>CI455</t>
+    <t>CI464</t>
+  </si>
+  <si>
+    <t>21470269</t>
+  </si>
+  <si>
+    <t>21470270</t>
+  </si>
+  <si>
+    <t>21422079</t>
+  </si>
+  <si>
+    <t>21453170</t>
+  </si>
+  <si>
+    <t>'21302240</t>
+  </si>
+  <si>
+    <t>21090112</t>
   </si>
   <si>
     <t>21302239</t>
   </si>
   <si>
-    <t>21470269</t>
-  </si>
-  <si>
     <t>20256318</t>
   </si>
   <si>
-    <t>21470270</t>
-  </si>
-  <si>
-    <t>21422079</t>
-  </si>
-  <si>
-    <t>21453170</t>
-  </si>
-  <si>
-    <t>'21302240</t>
-  </si>
-  <si>
-    <t>21090112</t>
-  </si>
-  <si>
     <t>21433484</t>
   </si>
   <si>
@@ -987,16 +1005,7 @@
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>CI434: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI435: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI436: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI437: PTN Lively Clean</t>
+    <t>CI437: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>CI438: H&amp;S Daily Clean Libra</t>
@@ -1005,25 +1014,22 @@
     <t>CI440: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI443: H&amp;S Daily Smooth Libra</t>
+    <t>CI442: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI445: H&amp;S Daily Smooth Libra</t>
   </si>
   <si>
     <t>REP02-0112: HC BASE</t>
   </si>
   <si>
-    <t>CI444: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI445: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI448: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI451: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI452: H&amp;S Daily Clean Libra</t>
+    <t>CI446: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI447: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI450: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>CI453: H&amp;S Daily Cool Libra</t>
@@ -1032,58 +1038,76 @@
     <t>CI454: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI456: H&amp;S Daily Cool Libra</t>
+    <t>CI455: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI456: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI458: H&amp;S Daily Cool Libra</t>
   </si>
   <si>
     <t>REP03-0112: HC BASE</t>
   </si>
   <si>
-    <t>CI457: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI458: PTN Silky Smooth Shampoo</t>
-  </si>
-  <si>
-    <t>CI459: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
     <t>CI460: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI461: H&amp;S SS</t>
+    <t>CI461: PTN Silky Smooth Shampoo</t>
   </si>
   <si>
     <t>CI462: H&amp;S Daily Cool Libra</t>
   </si>
   <si>
-    <t>CI433: PTN SS Conditioner</t>
+    <t>CI463: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI465: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI466: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI435: PTN SS Conditioner</t>
   </si>
   <si>
     <t>COND WASH (60m)</t>
   </si>
   <si>
-    <t>CI439: PTN SS Conditioner</t>
-  </si>
-  <si>
-    <t>CI441: H&amp;S Deep Cleanse</t>
-  </si>
-  <si>
-    <t>CI442: H&amp;S NEEM</t>
-  </si>
-  <si>
-    <t>CI446: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI447: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI449: H&amp;S SB</t>
-  </si>
-  <si>
-    <t>CI450: H&amp;S CM 2in1</t>
-  </si>
-  <si>
-    <t>CI455: H&amp;S AHF 2in1</t>
+    <t>CI441: PTN SS Conditioner</t>
+  </si>
+  <si>
+    <t>CI436: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI439: PTN Lively Clean</t>
+  </si>
+  <si>
+    <t>CI443: H&amp;S Deep Cleanse</t>
+  </si>
+  <si>
+    <t>CI444: H&amp;S NEEM</t>
+  </si>
+  <si>
+    <t>CI448: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI449: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI451: H&amp;S SB</t>
+  </si>
+  <si>
+    <t>CI452: H&amp;S CM 2in1</t>
+  </si>
+  <si>
+    <t>CI457: H&amp;S AHF 2in1</t>
+  </si>
+  <si>
+    <t>CI459: PTN Lively Clean</t>
+  </si>
+  <si>
+    <t>CI464: PTN  Hair Fall Control</t>
   </si>
   <si>
     <t>Sr.No</t>
@@ -1490,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="21" width="15.7109375" customWidth="1"/>
@@ -1563,55 +1587,55 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I2">
         <v>2.2948</v>
       </c>
       <c r="J2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L2" s="2">
-        <v>46033.375</v>
+        <v>46033.51388888889</v>
       </c>
       <c r="M2">
         <v>90</v>
       </c>
       <c r="N2" s="2">
-        <v>46033.4375</v>
+        <v>46033.57638888889</v>
       </c>
       <c r="O2">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q2" s="2">
-        <v>46033.83333333334</v>
+        <v>46033.95694444444</v>
       </c>
       <c r="R2" s="2">
-        <v>46033.875</v>
+        <v>46033.99861111111</v>
       </c>
       <c r="S2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1622,114 +1646,114 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I3">
-        <v>4.4891</v>
+        <v>4.4185</v>
       </c>
       <c r="J3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L3" s="2">
-        <v>46033.45138888889</v>
+        <v>46033.59027777778</v>
       </c>
       <c r="M3">
         <v>90</v>
       </c>
       <c r="N3" s="2">
-        <v>46033.51388888889</v>
+        <v>46033.65277777778</v>
       </c>
       <c r="O3">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="P3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q3" s="2">
-        <v>46033.95555555556</v>
+        <v>46034.08333333334</v>
       </c>
       <c r="R3" s="2">
-        <v>46035.71875</v>
+        <v>46034.26736111111</v>
       </c>
       <c r="S3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I4">
         <v>4.4185</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L4" s="2">
-        <v>46033.51388888889</v>
+        <v>46033.65277777778</v>
       </c>
       <c r="M4">
         <v>90</v>
       </c>
       <c r="N4" s="2">
-        <v>46033.57638888889</v>
+        <v>46033.71527777778</v>
       </c>
       <c r="O4">
-        <v>730</v>
+        <v>795</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q4" s="2">
-        <v>46034.08333333334</v>
+        <v>46034.26736111111</v>
       </c>
       <c r="R4" s="2">
-        <v>46034.26736111111</v>
+        <v>46034.45138888889</v>
       </c>
       <c r="S4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1740,55 +1764,55 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I5">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="J5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L5" s="2">
-        <v>46033.57638888889</v>
+        <v>46033.71527777778</v>
       </c>
       <c r="M5">
         <v>90</v>
       </c>
       <c r="N5" s="2">
-        <v>46033.63888888889</v>
+        <v>46033.77777777778</v>
       </c>
       <c r="O5">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q5" s="2">
-        <v>46034.26736111111</v>
+        <v>46034.40416666667</v>
       </c>
       <c r="R5" s="2">
-        <v>46034.45138888889</v>
+        <v>46034.61805555555</v>
       </c>
       <c r="S5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1802,116 +1826,116 @@
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I6">
-        <v>7.9415</v>
+        <v>4.4185</v>
       </c>
       <c r="J6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K6" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L6" s="2">
-        <v>46033.65277777778</v>
+        <v>46033.77777777778</v>
       </c>
       <c r="M6">
         <v>90</v>
       </c>
       <c r="N6" s="2">
-        <v>46033.71527777778</v>
+        <v>46033.84027777778</v>
       </c>
       <c r="O6">
-        <v>961</v>
+        <v>880</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q6" s="2">
-        <v>46034.38263888889</v>
+        <v>46034.45138888889</v>
       </c>
       <c r="R6" s="2">
-        <v>46035.59861111111</v>
+        <v>46034.63472222222</v>
       </c>
       <c r="S6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I7">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K7" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L7" s="2">
-        <v>46033.71527777778</v>
+        <v>46033.84027777778</v>
       </c>
       <c r="M7">
         <v>90</v>
       </c>
       <c r="N7" s="2">
-        <v>46033.77777777778</v>
+        <v>46033.90277777778</v>
       </c>
       <c r="O7">
-        <v>902</v>
+        <v>1030</v>
       </c>
       <c r="P7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q7" s="2">
-        <v>46034.40416666667</v>
+        <v>46034.61805555555</v>
       </c>
       <c r="R7" s="2">
-        <v>46034.61805555555</v>
+        <v>46034.83125</v>
       </c>
       <c r="S7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -1920,52 +1944,52 @@
         <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I8">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="J8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L8" s="2">
-        <v>46033.77777777778</v>
+        <v>46033.91666666666</v>
       </c>
       <c r="M8">
         <v>90</v>
       </c>
       <c r="N8" s="2">
-        <v>46033.84027777778</v>
+        <v>46033.97916666666</v>
       </c>
       <c r="O8">
-        <v>880</v>
+        <v>960</v>
       </c>
       <c r="P8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="Q8" s="2">
-        <v>46034.45138888889</v>
+        <v>46034.64583333334</v>
       </c>
       <c r="R8" s="2">
-        <v>46034.63472222222</v>
+        <v>46034.6875</v>
       </c>
       <c r="S8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1976,114 +2000,114 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I9">
-        <v>4.4185</v>
+        <v>5.2733</v>
       </c>
       <c r="J9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K9" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L9" s="2">
-        <v>46033.84027777778</v>
+        <v>46034.32638888889</v>
       </c>
       <c r="M9">
         <v>90</v>
       </c>
       <c r="N9" s="2">
-        <v>46033.90277777778</v>
+        <v>46034.38888888889</v>
       </c>
       <c r="O9">
-        <v>1030</v>
+        <v>382</v>
       </c>
       <c r="P9" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q9" s="2">
-        <v>46034.61805555555</v>
+        <v>46034.65416666667</v>
       </c>
       <c r="R9" s="2">
-        <v>46034.83125</v>
+        <v>46034.81111111111</v>
       </c>
       <c r="S9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I10">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="J10" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K10" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L10" s="2">
-        <v>46033.91666666666</v>
+        <v>46034.38888888889</v>
       </c>
       <c r="M10">
         <v>90</v>
       </c>
       <c r="N10" s="2">
-        <v>46033.97916666666</v>
+        <v>46034.45138888889</v>
       </c>
       <c r="O10">
-        <v>960</v>
+        <v>340</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q10" s="2">
-        <v>46034.64583333334</v>
+        <v>46034.6875</v>
       </c>
       <c r="R10" s="2">
-        <v>46034.6875</v>
+        <v>46034.87083333333</v>
       </c>
       <c r="S10" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2094,55 +2118,55 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
         <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I11">
-        <v>5.2733</v>
+        <v>4.4185</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L11" s="2">
-        <v>46034.32638888889</v>
+        <v>46034.45138888889</v>
       </c>
       <c r="M11">
         <v>90</v>
       </c>
       <c r="N11" s="2">
-        <v>46034.38888888889</v>
+        <v>46034.51388888889</v>
       </c>
       <c r="O11">
-        <v>382</v>
+        <v>514</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q11" s="2">
-        <v>46034.65416666667</v>
+        <v>46034.87083333333</v>
       </c>
       <c r="R11" s="2">
-        <v>46034.81111111111</v>
+        <v>46035.05486111111</v>
       </c>
       <c r="S11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2153,119 +2177,119 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I12">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="J12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L12" s="2">
-        <v>46034.38888888889</v>
+        <v>46034.51388888889</v>
       </c>
       <c r="M12">
         <v>90</v>
       </c>
       <c r="N12" s="2">
-        <v>46034.45138888889</v>
+        <v>46034.57638888889</v>
       </c>
       <c r="O12">
-        <v>340</v>
+        <v>521</v>
       </c>
       <c r="P12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q12" s="2">
-        <v>46034.6875</v>
+        <v>46034.93819444445</v>
       </c>
       <c r="R12" s="2">
-        <v>46034.87083333333</v>
+        <v>46035.15208333333</v>
       </c>
       <c r="S12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I13">
         <v>4.4185</v>
       </c>
       <c r="J13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L13" s="2">
-        <v>46034.45138888889</v>
+        <v>46034.57638888889</v>
       </c>
       <c r="M13">
         <v>90</v>
       </c>
       <c r="N13" s="2">
-        <v>46034.51388888889</v>
+        <v>46034.63888888889</v>
       </c>
       <c r="O13">
-        <v>514</v>
+        <v>599</v>
       </c>
       <c r="P13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q13" s="2">
-        <v>46034.87083333333</v>
+        <v>46035.05486111111</v>
       </c>
       <c r="R13" s="2">
-        <v>46035.05486111111</v>
+        <v>46035.23819444444</v>
       </c>
       <c r="S13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
@@ -2274,116 +2298,116 @@
         <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I14">
         <v>4.4163</v>
       </c>
       <c r="J14" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K14" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L14" s="2">
-        <v>46034.51388888889</v>
+        <v>46034.63888888889</v>
       </c>
       <c r="M14">
         <v>90</v>
       </c>
       <c r="N14" s="2">
-        <v>46034.57638888889</v>
+        <v>46034.70138888889</v>
       </c>
       <c r="O14">
-        <v>521</v>
+        <v>649</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q14" s="2">
-        <v>46034.93819444445</v>
+        <v>46035.15208333333</v>
       </c>
       <c r="R14" s="2">
-        <v>46035.15208333333</v>
+        <v>46035.36527777778</v>
       </c>
       <c r="S14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I15">
         <v>4.4185</v>
       </c>
       <c r="J15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L15" s="2">
-        <v>46034.57638888889</v>
+        <v>46034.70138888889</v>
       </c>
       <c r="M15">
         <v>90</v>
       </c>
       <c r="N15" s="2">
-        <v>46034.63888888889</v>
+        <v>46034.76388888889</v>
       </c>
       <c r="O15">
-        <v>599</v>
+        <v>683</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q15" s="2">
-        <v>46035.05486111111</v>
+        <v>46035.23819444444</v>
       </c>
       <c r="R15" s="2">
-        <v>46035.23819444444</v>
+        <v>46035.42222222222</v>
       </c>
       <c r="S15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -2392,57 +2416,57 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I16">
         <v>4.4163</v>
       </c>
       <c r="J16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K16" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L16" s="2">
-        <v>46034.63888888889</v>
+        <v>46034.76388888889</v>
       </c>
       <c r="M16">
         <v>90</v>
       </c>
       <c r="N16" s="2">
-        <v>46034.70138888889</v>
+        <v>46034.82638888889</v>
       </c>
       <c r="O16">
-        <v>649</v>
+        <v>776</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q16" s="2">
-        <v>46035.15208333333</v>
+        <v>46035.36527777778</v>
       </c>
       <c r="R16" s="2">
-        <v>46035.36527777778</v>
+        <v>46035.60625</v>
       </c>
       <c r="S16" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>39</v>
@@ -2451,170 +2475,170 @@
         <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I17">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="J17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L17" s="2">
-        <v>46034.70138888889</v>
+        <v>46034.84027777778</v>
       </c>
       <c r="M17">
         <v>90</v>
       </c>
       <c r="N17" s="2">
-        <v>46034.76388888889</v>
+        <v>46034.90277777778</v>
       </c>
       <c r="O17">
-        <v>683</v>
+        <v>722</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="Q17" s="2">
-        <v>46035.23819444444</v>
+        <v>46035.40416666667</v>
       </c>
       <c r="R17" s="2">
-        <v>46035.42222222222</v>
+        <v>46035.44583333333</v>
       </c>
       <c r="S17" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H18" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I18">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J18" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L18" s="2">
-        <v>46034.76388888889</v>
+        <v>46034.91666666666</v>
       </c>
       <c r="M18">
         <v>90</v>
       </c>
       <c r="N18" s="2">
-        <v>46034.82638888889</v>
+        <v>46034.97916666666</v>
       </c>
       <c r="O18">
-        <v>776</v>
+        <v>638</v>
       </c>
       <c r="P18" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q18" s="2">
-        <v>46035.36527777778</v>
+        <v>46035.42222222222</v>
       </c>
       <c r="R18" s="2">
-        <v>46035.60625</v>
+        <v>46035.63333333333</v>
       </c>
       <c r="S18" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H19" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I19">
-        <v>2.2948</v>
+        <v>2.9398</v>
       </c>
       <c r="J19" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L19" s="2">
-        <v>46034.84027777778</v>
+        <v>46035.34861111111</v>
       </c>
       <c r="M19">
         <v>90</v>
       </c>
       <c r="N19" s="2">
-        <v>46034.90277777778</v>
+        <v>46035.41111111111</v>
       </c>
       <c r="O19">
-        <v>722</v>
+        <v>270</v>
       </c>
       <c r="P19" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q19" s="2">
-        <v>46035.40416666667</v>
+        <v>46035.59861111111</v>
       </c>
       <c r="R19" s="2">
-        <v>46035.44583333333</v>
+        <v>46035.65902777778</v>
       </c>
       <c r="S19" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2625,55 +2649,55 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H20" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I20">
         <v>4.4185</v>
       </c>
       <c r="J20" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K20" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L20" s="2">
-        <v>46034.91666666666</v>
+        <v>46035.425</v>
       </c>
       <c r="M20">
         <v>90</v>
       </c>
       <c r="N20" s="2">
-        <v>46034.97916666666</v>
+        <v>46035.4875</v>
       </c>
       <c r="O20">
-        <v>638</v>
+        <v>171</v>
       </c>
       <c r="P20" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q20" s="2">
-        <v>46035.42222222222</v>
+        <v>46035.60625</v>
       </c>
       <c r="R20" s="2">
-        <v>46035.63333333333</v>
+        <v>46035.82013888889</v>
       </c>
       <c r="S20" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2684,55 +2708,55 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
         <v>131</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H21" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I21">
-        <v>2.9398</v>
+        <v>4.4185</v>
       </c>
       <c r="J21" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L21" s="2">
-        <v>46035.34861111111</v>
+        <v>46035.4875</v>
       </c>
       <c r="M21">
         <v>90</v>
       </c>
       <c r="N21" s="2">
-        <v>46035.41111111111</v>
+        <v>46035.55</v>
       </c>
       <c r="O21">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q21" s="2">
-        <v>46035.59861111111</v>
+        <v>46035.63333333333</v>
       </c>
       <c r="R21" s="2">
-        <v>46035.65902777778</v>
+        <v>46035.81736111111</v>
       </c>
       <c r="S21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2743,55 +2767,55 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I22">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="J22" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K22" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L22" s="2">
-        <v>46035.425</v>
+        <v>46035.57291666666</v>
       </c>
       <c r="M22">
         <v>90</v>
       </c>
       <c r="N22" s="2">
-        <v>46035.4875</v>
+        <v>46035.63541666666</v>
       </c>
       <c r="O22">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="P22" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q22" s="2">
-        <v>46035.60625</v>
+        <v>46035.71875</v>
       </c>
       <c r="R22" s="2">
-        <v>46035.82013888889</v>
+        <v>46035.83888888889</v>
       </c>
       <c r="S22" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2802,341 +2826,341 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I23">
         <v>4.4185</v>
       </c>
       <c r="J23" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K23" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L23" s="2">
-        <v>46035.4875</v>
+        <v>46035.67430555556</v>
       </c>
       <c r="M23">
         <v>90</v>
       </c>
       <c r="N23" s="2">
-        <v>46035.55</v>
+        <v>46035.73680555556</v>
       </c>
       <c r="O23">
         <v>120</v>
       </c>
       <c r="P23" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q23" s="2">
-        <v>46035.63333333333</v>
+        <v>46035.82013888889</v>
       </c>
       <c r="R23" s="2">
-        <v>46035.81736111111</v>
+        <v>46036.03402777778</v>
       </c>
       <c r="S23" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I24">
-        <v>4.5228</v>
+        <v>1.1202</v>
       </c>
       <c r="J24" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K24" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L24" s="2">
-        <v>46035.57291666666</v>
+        <v>46032.35486111111</v>
       </c>
       <c r="M24">
         <v>90</v>
       </c>
       <c r="N24" s="2">
-        <v>46035.63541666666</v>
+        <v>46032.41736111111</v>
       </c>
       <c r="O24">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q24" s="2">
-        <v>46035.71875</v>
+        <v>46033.41736111111</v>
       </c>
       <c r="R24" s="2">
-        <v>46035.83888888889</v>
+        <v>46034.43263888889</v>
       </c>
       <c r="S24" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I25">
-        <v>4.4185</v>
+        <v>0.28</v>
       </c>
       <c r="J25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K25" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L25" s="2">
-        <v>46035.67430555556</v>
+        <v>46032.87013888889</v>
       </c>
       <c r="M25">
         <v>90</v>
       </c>
       <c r="N25" s="2">
-        <v>46035.73680555556</v>
+        <v>46032.93263888889</v>
       </c>
       <c r="O25">
-        <v>120</v>
+        <v>2160</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q25" s="2">
-        <v>46035.82013888889</v>
+        <v>46034.43263888889</v>
       </c>
       <c r="R25" s="2">
-        <v>46036.03402777778</v>
+        <v>46034.59722222222</v>
       </c>
       <c r="S25" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G26" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I26">
-        <v>1.1202</v>
+        <v>2.2544</v>
       </c>
       <c r="J26" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L26" s="2">
-        <v>46032.35486111111</v>
+        <v>46032.97430555556</v>
       </c>
       <c r="M26">
         <v>90</v>
       </c>
       <c r="N26" s="2">
-        <v>46032.41736111111</v>
+        <v>46033.03680555556</v>
       </c>
       <c r="O26">
-        <v>1440</v>
+        <v>1323</v>
       </c>
       <c r="P26" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q26" s="2">
-        <v>46033.41736111111</v>
+        <v>46033.95555555556</v>
       </c>
       <c r="R26" s="2">
-        <v>46034.43263888889</v>
+        <v>46034.38263888889</v>
       </c>
       <c r="S26" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I27">
-        <v>0.28</v>
+        <v>2.1956</v>
       </c>
       <c r="J27" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K27" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L27" s="2">
-        <v>46032.47986111111</v>
+        <v>46033.32013888889</v>
       </c>
       <c r="M27">
         <v>90</v>
       </c>
       <c r="N27" s="2">
-        <v>46032.54236111111</v>
+        <v>46033.38263888889</v>
       </c>
       <c r="O27">
-        <v>2722</v>
+        <v>1440</v>
       </c>
       <c r="P27" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q27" s="2">
-        <v>46034.43263888889</v>
+        <v>46034.38263888889</v>
       </c>
       <c r="R27" s="2">
-        <v>46034.59722222222</v>
+        <v>46034.46527777778</v>
       </c>
       <c r="S27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H28" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I28">
         <v>2.2544</v>
       </c>
       <c r="J28" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K28" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L28" s="2">
-        <v>46032.58402777778</v>
+        <v>46033.40277777778</v>
       </c>
       <c r="M28">
         <v>90</v>
       </c>
       <c r="N28" s="2">
-        <v>46032.64652777778</v>
+        <v>46033.46527777778</v>
       </c>
       <c r="O28">
-        <v>2619</v>
+        <v>1440</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q28" s="2">
         <v>46034.46527777778</v>
@@ -3145,57 +3169,57 @@
         <v>46034.55972222222</v>
       </c>
       <c r="S28" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G29" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I29">
         <v>2.2544</v>
       </c>
       <c r="J29" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K29" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L29" s="2">
-        <v>46032.66041666667</v>
+        <v>46033.49722222222</v>
       </c>
       <c r="M29">
         <v>90</v>
       </c>
       <c r="N29" s="2">
-        <v>46032.72291666667</v>
+        <v>46033.55972222222</v>
       </c>
       <c r="O29">
-        <v>2645</v>
+        <v>1440</v>
       </c>
       <c r="P29" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q29" s="2">
         <v>46034.55972222222</v>
@@ -3204,57 +3228,57 @@
         <v>46034.65416666667</v>
       </c>
       <c r="S29" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
         <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G30" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I30">
         <v>2.2511</v>
       </c>
       <c r="J30" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L30" s="2">
-        <v>46032.74861111111</v>
+        <v>46033.74861111111</v>
       </c>
       <c r="M30">
         <v>90</v>
       </c>
       <c r="N30" s="2">
-        <v>46032.81111111111</v>
+        <v>46033.81111111111</v>
       </c>
       <c r="O30">
-        <v>2880</v>
+        <v>1440</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q30" s="2">
         <v>46034.81111111111</v>
@@ -3263,57 +3287,57 @@
         <v>46034.87152777778</v>
       </c>
       <c r="S30" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I31">
         <v>2.2082</v>
       </c>
       <c r="J31" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K31" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L31" s="2">
-        <v>46032.825</v>
+        <v>46033.825</v>
       </c>
       <c r="M31">
         <v>90</v>
       </c>
       <c r="N31" s="2">
-        <v>46032.8875</v>
+        <v>46033.8875</v>
       </c>
       <c r="O31">
-        <v>2799</v>
+        <v>1359</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q31" s="2">
         <v>46034.83125</v>
@@ -3322,57 +3346,57 @@
         <v>46034.93819444445</v>
       </c>
       <c r="S31" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I32">
         <v>2.2511</v>
       </c>
       <c r="J32" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K32" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L32" s="2">
-        <v>46032.90138888889</v>
+        <v>46033.90138888889</v>
       </c>
       <c r="M32">
         <v>90</v>
       </c>
       <c r="N32" s="2">
-        <v>46032.96388888889</v>
+        <v>46033.96388888889</v>
       </c>
       <c r="O32">
-        <v>2747</v>
+        <v>1307</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q32" s="2">
         <v>46034.87152777778</v>
@@ -3381,57 +3405,57 @@
         <v>46034.93194444444</v>
       </c>
       <c r="S32" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H33" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I33">
         <v>2.2511</v>
       </c>
       <c r="J33" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K33" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L33" s="2">
-        <v>46032.97777777778</v>
+        <v>46033.97777777778</v>
       </c>
       <c r="M33">
         <v>90</v>
       </c>
       <c r="N33" s="2">
-        <v>46033.04027777778</v>
+        <v>46034.04027777778</v>
       </c>
       <c r="O33">
-        <v>2724</v>
+        <v>1284</v>
       </c>
       <c r="P33" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q33" s="2">
         <v>46034.93194444444</v>
@@ -3440,57 +3464,57 @@
         <v>46035.325</v>
       </c>
       <c r="S33" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G34" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H34" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I34">
         <v>2.2511</v>
       </c>
       <c r="J34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K34" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L34" s="2">
-        <v>46033.2625</v>
+        <v>46034.2625</v>
       </c>
       <c r="M34">
         <v>90</v>
       </c>
       <c r="N34" s="2">
-        <v>46033.325</v>
+        <v>46034.325</v>
       </c>
       <c r="O34">
-        <v>2880</v>
+        <v>1440</v>
       </c>
       <c r="P34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q34" s="2">
         <v>46035.325</v>
@@ -3499,7 +3523,125 @@
         <v>46035.38541666666</v>
       </c>
       <c r="S34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" t="s">
+        <v>146</v>
+      </c>
+      <c r="H35" t="s">
+        <v>148</v>
+      </c>
+      <c r="I35">
+        <v>2.2163</v>
+      </c>
+      <c r="J35" t="s">
         <v>150</v>
+      </c>
+      <c r="K35" t="s">
+        <v>151</v>
+      </c>
+      <c r="L35" s="2">
+        <v>46034.35069444445</v>
+      </c>
+      <c r="M35">
+        <v>90</v>
+      </c>
+      <c r="N35" s="2">
+        <v>46034.41319444445</v>
+      </c>
+      <c r="O35">
+        <v>1440</v>
+      </c>
+      <c r="P35" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>46035.41319444445</v>
+      </c>
+      <c r="R35" s="2">
+        <v>46035.59861111111</v>
+      </c>
+      <c r="S35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36">
+        <v>2.2614</v>
+      </c>
+      <c r="J36" t="s">
+        <v>149</v>
+      </c>
+      <c r="K36" t="s">
+        <v>151</v>
+      </c>
+      <c r="L36" s="2">
+        <v>46034.59652777778</v>
+      </c>
+      <c r="M36">
+        <v>90</v>
+      </c>
+      <c r="N36" s="2">
+        <v>46034.65902777778</v>
+      </c>
+      <c r="O36">
+        <v>1440</v>
+      </c>
+      <c r="P36" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>46035.65902777778</v>
+      </c>
+      <c r="R36" s="2">
+        <v>46035.71875</v>
+      </c>
+      <c r="S36" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3519,304 +3661,250 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>348</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>348</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>348</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>347</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>347</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>349</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>349</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>349</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>350</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>350</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>350</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>322</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B22" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>351</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>351</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>351</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>322</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>352</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>352</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>352</v>
@@ -3824,1389 +3912,1470 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>355</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>355</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>355</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>151</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>151</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>321</v>
+        <v>151</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>321</v>
+        <v>151</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>321</v>
+        <v>151</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>322</v>
+        <v>151</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>323</v>
+        <v>151</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>323</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>323</v>
+        <v>151</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>331</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>331</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>231</v>
+      </c>
+      <c r="B73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>225</v>
-      </c>
-      <c r="B73" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="3" t="s">
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>232</v>
+      </c>
+      <c r="B74" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>234</v>
+      </c>
+      <c r="B76" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>226</v>
-      </c>
-      <c r="B74" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="3" t="s">
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>236</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>237</v>
+      </c>
+      <c r="B79" t="s">
+        <v>152</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>238</v>
+      </c>
+      <c r="B80" t="s">
+        <v>152</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>239</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>227</v>
-      </c>
-      <c r="B75" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>228</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>229</v>
-      </c>
-      <c r="B77" t="s">
-        <v>146</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>230</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>231</v>
-      </c>
-      <c r="B79" t="s">
-        <v>146</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>232</v>
-      </c>
-      <c r="B80" t="s">
-        <v>146</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>233</v>
-      </c>
-      <c r="B81" t="s">
-        <v>147</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B82" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B92" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B93" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B94" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>151</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B98" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B99" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B100" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
+        <v>336</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B102" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
+        <v>336</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B104" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B105" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B107" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B110" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
+        <v>339</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
+        <v>339</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
+        <v>340</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B114" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B119" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B121" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B122" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B123" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B124" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B125" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B126" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B127" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B130" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B151" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B152" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B153" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B154" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B155" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B156" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B157" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B158" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B159" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B160" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B161" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B163" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B164" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B167" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B168" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -5216,7 +5385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -5226,34 +5395,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5261,25 +5430,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5287,25 +5456,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5313,25 +5482,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5339,25 +5508,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5365,22 +5534,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J6" t="s">
         <v>60</v>
@@ -5391,25 +5560,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5417,22 +5586,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J8" t="s">
         <v>59</v>
@@ -5443,25 +5612,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5469,25 +5638,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5495,13 +5664,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>82</v>
@@ -5510,10 +5679,10 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5521,25 +5690,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5547,25 +5716,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5573,22 +5742,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J14" t="s">
         <v>64</v>
@@ -5599,25 +5768,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5625,22 +5794,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J16" t="s">
         <v>64</v>
@@ -5651,22 +5820,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J17" t="s">
         <v>59</v>
@@ -5677,25 +5846,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5703,25 +5872,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5729,25 +5898,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5755,25 +5924,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5781,25 +5950,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5807,25 +5976,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J23" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5833,25 +6002,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5859,25 +6028,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5885,25 +6054,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5911,25 +6080,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5937,25 +6106,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5963,25 +6132,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5989,25 +6158,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G30" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -6015,25 +6184,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -6041,25 +6210,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G32" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -6067,25 +6236,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -6093,25 +6262,77 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" t="s">
+        <v>146</v>
+      </c>
+      <c r="J34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>375</v>
+      </c>
+      <c r="C35" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" t="s">
         <v>138</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" t="s">
-        <v>140</v>
-      </c>
-      <c r="J34" t="s">
-        <v>76</v>
+      <c r="E35" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" t="s">
+        <v>146</v>
+      </c>
+      <c r="J35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>375</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" t="s">
+        <v>146</v>
+      </c>
+      <c r="J36" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
